--- a/data/trans_orig/P1431-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1431-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad de riñón en 2012</t>
+          <t>Población con diagnóstico de enfermedad de riñón en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18972</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422435</t>
+          <t>423405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>436169</t>
+          <t>436183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>302436</t>
+          <t>301961</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313367</t>
+          <t>313383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>732693</t>
+          <t>733167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>747632</t>
+          <t>747909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410665</t>
+          <t>410720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417853</t>
+          <t>417844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>332583</t>
+          <t>332654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>747394</t>
+          <t>746609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>755743</t>
+          <t>755817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18594</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615741</t>
+          <t>614719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626385</t>
+          <t>626318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250742</t>
+          <t>251991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259181</t>
+          <t>259195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>870950</t>
+          <t>871097</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>883634</t>
+          <t>884434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26764</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40678</t>
+          <t>41555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1132245</t>
+          <t>1132544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1149433</t>
+          <t>1149280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>744559</t>
+          <t>745270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>758693</t>
+          <t>758679</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1883053</t>
+          <t>1882176</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1904470</t>
+          <t>1903864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14086</t>
+          <t>15915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>20778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>29963</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>496510</t>
+          <t>494681</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507408</t>
+          <t>507388</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739242</t>
+          <t>739468</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>753916</t>
+          <t>753355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1240928</t>
+          <t>1240880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1258252</t>
+          <t>1258272</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30342</t>
+          <t>32286</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32544</t>
+          <t>32302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260305</t>
+          <t>259936</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1077901</t>
+          <t>1075957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1095861</t>
+          <t>1095268</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1342581</t>
+          <t>1342823</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1360663</t>
+          <t>1360718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30113</t>
+          <t>30213</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57391</t>
+          <t>55158</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40802</t>
+          <t>40023</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69815</t>
+          <t>69260</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74248</t>
+          <t>75856</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114115</t>
+          <t>114716</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3364519</t>
+          <t>3366752</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3391797</t>
+          <t>3391697</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3475991</t>
+          <t>3476546</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3505004</t>
+          <t>3505783</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6853601</t>
+          <t>6853000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6893468</t>
+          <t>6891860</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad de riñón en 2016</t>
+          <t>Población con diagnóstico de enfermedad de riñón en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23033</t>
+          <t>22220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409462</t>
+          <t>409239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423659</t>
+          <t>423453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339616</t>
+          <t>340424</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>753114</t>
+          <t>753927</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>769002</t>
+          <t>769161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369258</t>
+          <t>369054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376468</t>
+          <t>376470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365607</t>
+          <t>365422</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738505</t>
+          <t>739164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747555</t>
+          <t>747777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>15089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510779</t>
+          <t>511090</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520000</t>
+          <t>519965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157990</t>
+          <t>158143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>674261</t>
+          <t>672947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>684921</t>
+          <t>684962</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18944</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>14532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29138</t>
+          <t>30380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1130694</t>
+          <t>1129867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144269</t>
+          <t>1143477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>810979</t>
+          <t>811344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>822599</t>
+          <t>822711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946376</t>
+          <t>1945134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1963877</t>
+          <t>1964305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>22821</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19584</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41619</t>
+          <t>42027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>597611</t>
+          <t>598005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>612170</t>
+          <t>612672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>714597</t>
+          <t>715423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>730551</t>
+          <t>731037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1317331</t>
+          <t>1316923</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1339366</t>
+          <t>1339863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18886</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40872</t>
+          <t>41279</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19789</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>42561</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281744</t>
+          <t>282353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1041153</t>
+          <t>1040746</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1063139</t>
+          <t>1062477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1326764</t>
+          <t>1326609</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1349381</t>
+          <t>1348334</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>33448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60853</t>
+          <t>60726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44078</t>
+          <t>41830</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75204</t>
+          <t>74274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84877</t>
+          <t>84736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126542</t>
+          <t>125519</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3324869</t>
+          <t>3324996</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3352008</t>
+          <t>3352274</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3456392</t>
+          <t>3457322</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3487518</t>
+          <t>3489766</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6790776</t>
+          <t>6791799</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6832441</t>
+          <t>6832582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1431-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1431-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18498</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423405</t>
+          <t>422699</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>436183</t>
+          <t>436188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301961</t>
+          <t>302436</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313383</t>
+          <t>313381</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>733167</t>
+          <t>733209</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>747909</t>
+          <t>747765</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410720</t>
+          <t>409427</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417844</t>
+          <t>417857</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>332654</t>
+          <t>331654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>746609</t>
+          <t>746641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>755817</t>
+          <t>755748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>478</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614719</t>
+          <t>614863</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626318</t>
+          <t>626375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251991</t>
+          <t>252456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259195</t>
+          <t>259651</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>871097</t>
+          <t>871073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>884434</t>
+          <t>884372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26465</t>
+          <t>27753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19452</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41555</t>
+          <t>40388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1132544</t>
+          <t>1131256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1149280</t>
+          <t>1149229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>745270</t>
+          <t>745001</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>758679</t>
+          <t>758720</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1882176</t>
+          <t>1883343</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1903864</t>
+          <t>1904950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15915</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20778</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29963</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>494681</t>
+          <t>495286</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507388</t>
+          <t>507300</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739468</t>
+          <t>738765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>753355</t>
+          <t>753238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1240880</t>
+          <t>1240595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1258272</t>
+          <t>1258374</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32286</t>
+          <t>31313</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32302</t>
+          <t>33542</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259936</t>
+          <t>260579</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1075957</t>
+          <t>1076930</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1095268</t>
+          <t>1095573</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1342823</t>
+          <t>1341583</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1360718</t>
+          <t>1360513</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30213</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55158</t>
+          <t>56358</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40023</t>
+          <t>40250</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69260</t>
+          <t>68801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75856</t>
+          <t>76131</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114716</t>
+          <t>114829</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3366752</t>
+          <t>3365552</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3391697</t>
+          <t>3392781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3476546</t>
+          <t>3477005</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3505783</t>
+          <t>3505556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6853000</t>
+          <t>6852887</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6891860</t>
+          <t>6891585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19853</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22220</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409239</t>
+          <t>408937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423453</t>
+          <t>423294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340424</t>
+          <t>340480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>753927</t>
+          <t>753773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>769161</t>
+          <t>768863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>767</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369054</t>
+          <t>369473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376470</t>
+          <t>376460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365422</t>
+          <t>365454</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739164</t>
+          <t>738965</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747777</t>
+          <t>747762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15089</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511090</t>
+          <t>510886</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519965</t>
+          <t>520056</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158143</t>
+          <t>158408</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672947</t>
+          <t>673276</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>684962</t>
+          <t>684874</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>11590</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30380</t>
+          <t>28804</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1129867</t>
+          <t>1130757</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1143477</t>
+          <t>1144229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>811344</t>
+          <t>810731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>822711</t>
+          <t>822744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1945134</t>
+          <t>1946710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1964305</t>
+          <t>1963924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>23440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>23136</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42027</t>
+          <t>40622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>598005</t>
+          <t>597266</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>612672</t>
+          <t>612120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715423</t>
+          <t>715108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>731037</t>
+          <t>730907</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1316923</t>
+          <t>1318328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1339863</t>
+          <t>1340129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>19589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41279</t>
+          <t>40790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20836</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>43407</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282353</t>
+          <t>282374</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1040746</t>
+          <t>1041235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1062477</t>
+          <t>1062436</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1326609</t>
+          <t>1325763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1348334</t>
+          <t>1348708</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33448</t>
+          <t>32952</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60726</t>
+          <t>61486</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,82 +5439,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>56826</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>43341</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>74308</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>102298</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>82792</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>123953</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>1,79%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>56826</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>41830</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>74274</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>102298</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>84736</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>125519</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3324996</t>
+          <t>3324236</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3352274</t>
+          <t>3352770</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,82 +5552,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3275</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3474770</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3457288</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3488255</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,9%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6454</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6815020</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6793365</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6834526</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>98,21%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3275</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3474770</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3457322</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3489766</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6454</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6815020</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6791799</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6832582</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
